--- a/registry/TSP Register.xlsx
+++ b/registry/TSP Register.xlsx
@@ -451,8 +451,8 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
@@ -493,12 +493,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Primary AF</t>
+          <t>Primary Area</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Other AFs</t>
+          <t>Other Areas</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>TSP/TSP.1 WBS Register/DF.1 - WBS Register.md</t>
+          <t>TSP/TSP.1 WBS Register/TF.1 - WBS Register.md</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>TSP/TSP.2 RAID Register/DF.2 - RAID Register.md</t>
+          <t>TSP/TSP.2 RAID Register/TF.2 - RAID Register.md</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>TSP/TSP.3 TSP Register/DF.3 - TSP Register.md</t>
+          <t>TSP/TSP.3 TSP Register/TF.3 - TSP Register.md</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ready to adopt. Open item: Primary AF vocabulary still to be renamed.</t>
+          <t>Ready to adopt. Open item: Primary Area vocabulary resolved.</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">

--- a/registry/TSP Register.xlsx
+++ b/registry/TSP Register.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>TSP/TSP.1 WBS Register/TF.1 - WBS Register.md</t>
+          <t>TSP/TSP.1 WBS Register/TD.1 - WBS Register.md</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>TSP/TSP.2 RAID Register/TF.2 - RAID Register.md</t>
+          <t>TSP/TSP.2 RAID Register/TD.2 - RAID Register.md</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>TSP/TSP.3 TSP Register/TF.3 - TSP Register.md</t>
+          <t>TSP/TSP.3 TSP Register/TD.3 - TSP Register.md</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">

--- a/registry/TSP Register.xlsx
+++ b/registry/TSP Register.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,6 @@
           <t>Project management</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -620,7 +619,6 @@
           <t>Project management</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -679,7 +677,6 @@
           <t>Tool management</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -703,6 +700,61 @@
           <t>tsp-manager</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tool Installer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Vendors a tool from this catalogue into a project, records where the copy came from, and keeps it reconcilable with upstream: drift detection and three-way updates.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tool management</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TSP/TSP.4 Tool Installer/TD.4 - Tool Installer.md</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Ready to adopt. No skill by design - it runs at moments where a human decides.</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
@@ -856,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -902,6 +954,24 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>Register created for the AKOS catalogue. Seeded with the three tools published in this repository. This register is itself an instance of TSP.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TSP Register</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TSP.4 Tool Installer registered. First entry with no skill - recorded to show the register handles tools whose value is not an agent interface.</t>
         </is>
       </c>
     </row>

--- a/registry/TSP Register.xlsx
+++ b/registry/TSP Register.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -735,7 +735,6 @@
           <t>Tool management</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -754,7 +753,65 @@
       <c r="L5" s="4" t="n">
         <v>46265</v>
       </c>
-      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Artifact Register</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Inventory of the artifacts belonging to a scope - documents, folders, tools and physical items - recording what each is, where it lives digitally and physically, what contains it, and which tool governs its contents. The register assigns an ID that is written onto the artifact itself, so its claims about the filesystem can be checked.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Reference management</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TSP/TSP.5 Artifact Register/TD.5 - Artifact Register.md</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Ready to adopt. The only tool here that reconciles against reality rather than itself.</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>artifact-register</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
@@ -908,7 +965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -972,6 +1029,24 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>TSP.4 Tool Installer registered. First entry with no skill - recorded to show the register handles tools whose value is not an agent interface.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Artifact Register</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TSP.5 registered. Generalised from a personal reference-material system and a per-project document control list that turned out to be one tool at two scopes.</t>
         </is>
       </c>
     </row>
